--- a/북원_후원업체_지도관리.xlsx
+++ b/북원_후원업체_지도관리.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -653,6 +653,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,6 +710,16 @@
       <c r="H4" s="8" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>후원내용</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>소개</t>
         </is>
       </c>
     </row>

--- a/북원_후원업체_지도관리.xlsx
+++ b/북원_후원업체_지도관리.xlsx
@@ -486,7 +486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1059,28 +1059,28 @@
         <v>O</v>
       </c>
       <c r="B21" t="str">
-        <v>원주상공회의소</v>
+        <v>한국주택금융공사 강원서부지사</v>
       </c>
       <c r="C21" t="str">
-        <v>협회</v>
+        <v>공사</v>
       </c>
       <c r="D21" t="str">
-        <v>강원 원주시 북원로 2551 원주상공회의소</v>
+        <v>강원 춘천시 경춘로 2370 한국교직원공제회 강원회관 4층</v>
       </c>
       <c r="E21" t="str">
-        <v>033-743-2991</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>37.8647561810117</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>127.721042675305</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>쌀</v>
+        <v/>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1091,22 +1091,22 @@
         <v>O</v>
       </c>
       <c r="B22" t="str">
-        <v>한국주택금융공사 강원서부지사</v>
+        <v>오일상사</v>
       </c>
       <c r="C22" t="str">
-        <v>공사</v>
+        <v>기업</v>
       </c>
       <c r="D22" t="str">
-        <v>강원 춘천시 경춘로 2370 한국교직원공제회 강원회관 4층</v>
+        <v>강원 원주시 현충로 304-2</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>033-747-5134</v>
       </c>
       <c r="F22" t="str">
-        <v>37.8647561810117</v>
+        <v>37.3802582458272</v>
       </c>
       <c r="G22" t="str">
-        <v>127.721042675305</v>
+        <v>127.948646333947</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1123,22 +1123,22 @@
         <v>O</v>
       </c>
       <c r="B23" t="str">
-        <v>오일상사</v>
+        <v>(주)우진</v>
       </c>
       <c r="C23" t="str">
         <v>기업</v>
       </c>
       <c r="D23" t="str">
-        <v>강원 원주시 현충로 304-2</v>
+        <v>강원 원주시 태장공단길 50</v>
       </c>
       <c r="E23" t="str">
-        <v>033-747-5134</v>
+        <v>033-761-4243</v>
       </c>
       <c r="F23" t="str">
-        <v>37.3802582458272</v>
+        <v>37.4042680374089</v>
       </c>
       <c r="G23" t="str">
-        <v>127.948646333947</v>
+        <v>127.945785707146</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1155,22 +1155,22 @@
         <v>O</v>
       </c>
       <c r="B24" t="str">
-        <v>(주)우진</v>
+        <v>강원부품(주)</v>
       </c>
       <c r="C24" t="str">
         <v>기업</v>
       </c>
       <c r="D24" t="str">
-        <v>강원 원주시 태장공단길 50</v>
+        <v>강원 원주시 현충로 214</v>
       </c>
       <c r="E24" t="str">
-        <v>033-761-4243</v>
+        <v>033-743-1850</v>
       </c>
       <c r="F24" t="str">
-        <v>37.4042680374089</v>
+        <v>37.3728026159565</v>
       </c>
       <c r="G24" t="str">
-        <v>127.945785707146</v>
+        <v>127.950330853967</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1187,22 +1187,22 @@
         <v>O</v>
       </c>
       <c r="B25" t="str">
-        <v>강원부품(주)</v>
+        <v>떡빚는마을</v>
       </c>
       <c r="C25" t="str">
-        <v>기업</v>
+        <v>떡</v>
       </c>
       <c r="D25" t="str">
-        <v>강원 원주시 현충로 214</v>
+        <v>강원 원주시 흥양로 62</v>
       </c>
       <c r="E25" t="str">
-        <v>033-743-1850</v>
+        <v>033-900-7004</v>
       </c>
       <c r="F25" t="str">
-        <v>37.3728026159565</v>
+        <v>37.3830659998128</v>
       </c>
       <c r="G25" t="str">
-        <v>127.950330853967</v>
+        <v>127.954257184894</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1219,22 +1219,22 @@
         <v>O</v>
       </c>
       <c r="B26" t="str">
-        <v>떡빚는마을</v>
+        <v>한국광해광업공단</v>
       </c>
       <c r="C26" t="str">
-        <v>떡</v>
+        <v>공단</v>
       </c>
       <c r="D26" t="str">
-        <v>강원 원주시 흥양로 62</v>
+        <v>강원 원주시 혁신로 199</v>
       </c>
       <c r="E26" t="str">
-        <v>033-900-7004</v>
+        <v>033-736-5254</v>
       </c>
       <c r="F26" t="str">
-        <v>37.3830659998128</v>
+        <v>37.3256602608297</v>
       </c>
       <c r="G26" t="str">
-        <v>127.954257184894</v>
+        <v>127.991716831249</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -1251,22 +1251,22 @@
         <v>O</v>
       </c>
       <c r="B27" t="str">
-        <v>한국광해광업공단</v>
+        <v>밥상공동체 연탄은행</v>
       </c>
       <c r="C27" t="str">
-        <v>공단</v>
+        <v>복지재단</v>
       </c>
       <c r="D27" t="str">
-        <v>강원 원주시 혁신로 199</v>
+        <v>강원 원주시 평원로 6</v>
       </c>
       <c r="E27" t="str">
-        <v>033-736-5254</v>
+        <v>1577-9044</v>
       </c>
       <c r="F27" t="str">
-        <v>37.3256602608297</v>
+        <v>37.3480063267531</v>
       </c>
       <c r="G27" t="str">
-        <v>127.991716831249</v>
+        <v>127.954004773908</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1283,22 +1283,22 @@
         <v>O</v>
       </c>
       <c r="B28" t="str">
-        <v>밥상공동체 연탄은행</v>
+        <v>청산광고</v>
       </c>
       <c r="C28" t="str">
-        <v>복지재단</v>
+        <v>광고</v>
       </c>
       <c r="D28" t="str">
-        <v>강원 원주시 평원로 6</v>
+        <v>강원 원주시 샘둔지길 10</v>
       </c>
       <c r="E28" t="str">
-        <v>1577-9044</v>
+        <v>033-763-4400</v>
       </c>
       <c r="F28" t="str">
-        <v>37.3480063267531</v>
+        <v>37.3468267992581</v>
       </c>
       <c r="G28" t="str">
-        <v>127.954004773908</v>
+        <v>127.935997538842</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1315,22 +1315,22 @@
         <v>O</v>
       </c>
       <c r="B29" t="str">
-        <v>청산광고</v>
+        <v>나래프린트</v>
       </c>
       <c r="C29" t="str">
         <v>광고</v>
       </c>
       <c r="D29" t="str">
-        <v>강원 원주시 샘둔지길 10</v>
+        <v>강원 원주시 봉화로 173</v>
       </c>
       <c r="E29" t="str">
-        <v>033-763-4400</v>
+        <v>033-746-0852</v>
       </c>
       <c r="F29" t="str">
-        <v>37.3468267992581</v>
+        <v>37.3600411433857</v>
       </c>
       <c r="G29" t="str">
-        <v>127.935997538842</v>
+        <v>127.929007489512</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1347,22 +1347,22 @@
         <v>O</v>
       </c>
       <c r="B30" t="str">
-        <v>나래프린트</v>
+        <v>한국도로교통공단</v>
       </c>
       <c r="C30" t="str">
-        <v>광고</v>
+        <v>공단</v>
       </c>
       <c r="D30" t="str">
-        <v>강원 원주시 봉화로 173</v>
+        <v>강원특별자치도 원주시 혁신로 2 한국도로교통공단 본부</v>
       </c>
       <c r="E30" t="str">
-        <v>033-746-0852</v>
+        <v>1577-1120</v>
       </c>
       <c r="F30" t="str">
-        <v>37.3600411433857</v>
+        <v>37.3244992551977</v>
       </c>
       <c r="G30" t="str">
-        <v>127.929007489512</v>
+        <v>127.97535913134</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -1371,44 +1371,12 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>O</v>
-      </c>
-      <c r="B31" t="str">
-        <v>한국도로교통공단</v>
-      </c>
-      <c r="C31" t="str">
-        <v>공단</v>
-      </c>
-      <c r="D31" t="str">
-        <v>강원특별자치도 원주시 혁신로 2 한국도로교통공단 본부</v>
-      </c>
-      <c r="E31" t="str">
-        <v>1577-1120</v>
-      </c>
-      <c r="F31" t="str">
-        <v>37.3244992551977</v>
-      </c>
-      <c r="G31" t="str">
-        <v>127.97535913134</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
-      <c r="J31" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J30"/>
   </ignoredErrors>
 </worksheet>
 </file>